--- a/samples/ministry_sample.xlsx
+++ b/samples/ministry_sample.xlsx
@@ -666,9 +666,11 @@
       <c r="H6" s="3"/>
       <c r="I6">
         <f>SUM(E6:H6)</f>
+        <v>0</v>
       </c>
       <c r="J6">
         <f>IF(I6&gt;=72,"أ",IF(I6&gt;=64,"ب",IF(I6&gt;=52,"ج",IF(I6&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K6" s="4"/>
     </row>
@@ -691,9 +693,11 @@
       <c r="H7" s="3"/>
       <c r="I7">
         <f>SUM(E7:H7)</f>
+        <v>0</v>
       </c>
       <c r="J7">
         <f>IF(I7&gt;=72,"أ",IF(I7&gt;=64,"ب",IF(I7&gt;=52,"ج",IF(I7&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K7" s="4"/>
     </row>
@@ -716,9 +720,11 @@
       <c r="H8" s="3"/>
       <c r="I8">
         <f>SUM(E8:H8)</f>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>IF(I8&gt;=72,"أ",IF(I8&gt;=64,"ب",IF(I8&gt;=52,"ج",IF(I8&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K8" s="4"/>
     </row>
@@ -741,9 +747,11 @@
       <c r="H9" s="3"/>
       <c r="I9">
         <f>SUM(E9:H9)</f>
+        <v>0</v>
       </c>
       <c r="J9">
         <f>IF(I9&gt;=72,"أ",IF(I9&gt;=64,"ب",IF(I9&gt;=52,"ج",IF(I9&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K9" s="4"/>
     </row>
@@ -766,9 +774,11 @@
       <c r="H10" s="3"/>
       <c r="I10">
         <f>SUM(E10:H10)</f>
+        <v>0</v>
       </c>
       <c r="J10">
         <f>IF(I10&gt;=72,"أ",IF(I10&gt;=64,"ب",IF(I10&gt;=52,"ج",IF(I10&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K10" s="4"/>
     </row>
@@ -791,9 +801,11 @@
       <c r="H11" s="3"/>
       <c r="I11">
         <f>SUM(E11:H11)</f>
+        <v>0</v>
       </c>
       <c r="J11">
         <f>IF(I11&gt;=72,"أ",IF(I11&gt;=64,"ب",IF(I11&gt;=52,"ج",IF(I11&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K11" s="4"/>
     </row>
@@ -816,9 +828,11 @@
       <c r="H12" s="3"/>
       <c r="I12">
         <f>SUM(E12:H12)</f>
+        <v>0</v>
       </c>
       <c r="J12">
         <f>IF(I12&gt;=72,"أ",IF(I12&gt;=64,"ب",IF(I12&gt;=52,"ج",IF(I12&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K12" s="4"/>
     </row>
@@ -841,9 +855,11 @@
       <c r="H13" s="3"/>
       <c r="I13">
         <f>SUM(E13:H13)</f>
+        <v>0</v>
       </c>
       <c r="J13">
         <f>IF(I13&gt;=72,"أ",IF(I13&gt;=64,"ب",IF(I13&gt;=52,"ج",IF(I13&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K13" s="4"/>
     </row>
@@ -866,9 +882,11 @@
       <c r="H14" s="3"/>
       <c r="I14">
         <f>SUM(E14:H14)</f>
+        <v>0</v>
       </c>
       <c r="J14">
         <f>IF(I14&gt;=72,"أ",IF(I14&gt;=64,"ب",IF(I14&gt;=52,"ج",IF(I14&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K14" s="4"/>
     </row>
@@ -891,9 +909,11 @@
       <c r="H15" s="3"/>
       <c r="I15">
         <f>SUM(E15:H15)</f>
+        <v>0</v>
       </c>
       <c r="J15">
         <f>IF(I15&gt;=72,"أ",IF(I15&gt;=64,"ب",IF(I15&gt;=52,"ج",IF(I15&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K15" s="4"/>
     </row>
@@ -916,9 +936,11 @@
       <c r="H16" s="3"/>
       <c r="I16">
         <f>SUM(E16:H16)</f>
+        <v>0</v>
       </c>
       <c r="J16">
         <f>IF(I16&gt;=72,"أ",IF(I16&gt;=64,"ب",IF(I16&gt;=52,"ج",IF(I16&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K16" s="4"/>
     </row>
@@ -941,9 +963,11 @@
       <c r="H17" s="3"/>
       <c r="I17">
         <f>SUM(E17:H17)</f>
+        <v>0</v>
       </c>
       <c r="J17">
         <f>IF(I17&gt;=72,"أ",IF(I17&gt;=64,"ب",IF(I17&gt;=52,"ج",IF(I17&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K17" s="4"/>
     </row>
@@ -966,9 +990,11 @@
       <c r="H18" s="3"/>
       <c r="I18">
         <f>SUM(E18:H18)</f>
+        <v>0</v>
       </c>
       <c r="J18">
         <f>IF(I18&gt;=72,"أ",IF(I18&gt;=64,"ب",IF(I18&gt;=52,"ج",IF(I18&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K18" s="4"/>
     </row>
@@ -991,9 +1017,11 @@
       <c r="H19" s="3"/>
       <c r="I19">
         <f>SUM(E19:H19)</f>
+        <v>0</v>
       </c>
       <c r="J19">
         <f>IF(I19&gt;=72,"أ",IF(I19&gt;=64,"ب",IF(I19&gt;=52,"ج",IF(I19&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K19" s="4"/>
     </row>
@@ -1016,9 +1044,11 @@
       <c r="H20" s="3"/>
       <c r="I20">
         <f>SUM(E20:H20)</f>
+        <v>0</v>
       </c>
       <c r="J20">
         <f>IF(I20&gt;=72,"أ",IF(I20&gt;=64,"ب",IF(I20&gt;=52,"ج",IF(I20&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K20" s="4"/>
     </row>
@@ -1041,9 +1071,11 @@
       <c r="H21" s="3"/>
       <c r="I21">
         <f>SUM(E21:H21)</f>
+        <v>0</v>
       </c>
       <c r="J21">
         <f>IF(I21&gt;=72,"أ",IF(I21&gt;=64,"ب",IF(I21&gt;=52,"ج",IF(I21&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K21" s="4"/>
     </row>
@@ -1066,9 +1098,11 @@
       <c r="H22" s="3"/>
       <c r="I22">
         <f>SUM(E22:H22)</f>
+        <v>0</v>
       </c>
       <c r="J22">
         <f>IF(I22&gt;=72,"أ",IF(I22&gt;=64,"ب",IF(I22&gt;=52,"ج",IF(I22&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K22" s="4"/>
     </row>
@@ -1091,9 +1125,11 @@
       <c r="H23" s="3"/>
       <c r="I23">
         <f>SUM(E23:H23)</f>
+        <v>0</v>
       </c>
       <c r="J23">
         <f>IF(I23&gt;=72,"أ",IF(I23&gt;=64,"ب",IF(I23&gt;=52,"ج",IF(I23&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K23" s="4"/>
     </row>
@@ -1116,9 +1152,11 @@
       <c r="H24" s="3"/>
       <c r="I24">
         <f>SUM(E24:H24)</f>
+        <v>0</v>
       </c>
       <c r="J24">
         <f>IF(I24&gt;=72,"أ",IF(I24&gt;=64,"ب",IF(I24&gt;=52,"ج",IF(I24&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K24" s="4"/>
     </row>
@@ -1141,9 +1179,11 @@
       <c r="H25" s="3"/>
       <c r="I25">
         <f>SUM(E25:H25)</f>
+        <v>0</v>
       </c>
       <c r="J25">
         <f>IF(I25&gt;=72,"أ",IF(I25&gt;=64,"ب",IF(I25&gt;=52,"ج",IF(I25&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K25" s="4"/>
     </row>
@@ -1166,9 +1206,11 @@
       <c r="H26" s="3"/>
       <c r="I26">
         <f>SUM(E26:H26)</f>
+        <v>0</v>
       </c>
       <c r="J26">
         <f>IF(I26&gt;=72,"أ",IF(I26&gt;=64,"ب",IF(I26&gt;=52,"ج",IF(I26&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K26" s="4"/>
     </row>
@@ -1191,9 +1233,11 @@
       <c r="H27" s="3"/>
       <c r="I27">
         <f>SUM(E27:H27)</f>
+        <v>0</v>
       </c>
       <c r="J27">
         <f>IF(I27&gt;=72,"أ",IF(I27&gt;=64,"ب",IF(I27&gt;=52,"ج",IF(I27&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K27" s="4"/>
     </row>
@@ -1216,9 +1260,11 @@
       <c r="H28" s="3"/>
       <c r="I28">
         <f>SUM(E28:H28)</f>
+        <v>0</v>
       </c>
       <c r="J28">
         <f>IF(I28&gt;=72,"أ",IF(I28&gt;=64,"ب",IF(I28&gt;=52,"ج",IF(I28&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K28" s="4"/>
     </row>
@@ -1241,9 +1287,11 @@
       <c r="H29" s="3"/>
       <c r="I29">
         <f>SUM(E29:H29)</f>
+        <v>0</v>
       </c>
       <c r="J29">
         <f>IF(I29&gt;=72,"أ",IF(I29&gt;=64,"ب",IF(I29&gt;=52,"ج",IF(I29&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K29" s="4"/>
     </row>
@@ -1266,9 +1314,11 @@
       <c r="H30" s="3"/>
       <c r="I30">
         <f>SUM(E30:H30)</f>
+        <v>0</v>
       </c>
       <c r="J30">
         <f>IF(I30&gt;=72,"أ",IF(I30&gt;=64,"ب",IF(I30&gt;=52,"ج",IF(I30&gt;=40,"د","هـ"))))</f>
+        <v>0</v>
       </c>
       <c r="K30" s="4"/>
     </row>
@@ -1278,10 +1328,11 @@
       </c>
       <c r="I32">
         <f>IFERROR(AVERAGE(I6:I30),"")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="Xp5zktJfV+65ANhm3foSV7rxZSvGWO8v9gjeVLsMXM+QDE26CqE+cBQ/Bs73InR5IZpW645cL1WFvLKVWadLHw==" saltValue="zxxtny63T6XF9z4LKdlWww==" spinCount="100000"/>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="75pbrOJcSfqHHs/Bs2Qy2Pn+nwSs1aHZumjnxLL6CIJpfHzNlaZbD0b7StL7IfWwy3o3I1WgGeVh15pEhokkhw==" saltValue="aUfObxs29Gt48f+3uFbKlQ==" spinCount="100000"/>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1327,7 +1378,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="pJMuZ9e9fW7pjRLalooqcVlMQy1zIx7RHcUp1osPU4bhWNGPib+b6aA0ci4DCsqQzMVQrIn7PVR4lvE64m05qw==" saltValue="5gvDw8PWXgqH8aYYFdDETg==" spinCount="100000"/>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="W/OYgz793Di7eoL/LxirsTLFarFuQI30bxUXqiWuPoIJgIbCIUamdvOWlp9lipfWyVdzhgdf/T3Z3XmfWWPIOg==" saltValue="vWWqtKxwdlBWMKlvgZn+Cg==" spinCount="100000"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
